--- a/logs/experiments_not_systematic/sorted_by_experiment/4_lr_and_perturbation_search.xlsx
+++ b/logs/experiments_not_systematic/sorted_by_experiment/4_lr_and_perturbation_search.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/sorted_by_experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/sorted_by_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52BAEE78-3714-4FC8-9C94-37FACE259482}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68C725FE-58C0-4C05-94DF-49D0E402006E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="136">
   <si>
     <t>date</t>
   </si>
@@ -596,7 +596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -613,6 +613,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,6 +641,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main_results"/>
@@ -815,10 +822,14 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="[3, 4, 2]"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="map" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="1">
+        <s v="[0, 1, 2]"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="reorder" numFmtId="0">
       <sharedItems/>
@@ -1079,8 +1090,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1176,8 +1187,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1273,8 +1284,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1370,8 +1381,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1467,8 +1478,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1564,8 +1575,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1661,8 +1672,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1758,8 +1769,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1855,8 +1866,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -1952,8 +1963,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2049,8 +2060,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2146,8 +2157,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2243,8 +2254,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2340,8 +2351,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2437,8 +2448,8 @@
     <s v="compact"/>
     <s v="['effsu2', 'effsu2', 'realamplitudes']"/>
     <s v="full"/>
-    <s v="[3, 4, 2]"/>
-    <s v="[0, 1, 2]"/>
+    <x v="0"/>
+    <x v="0"/>
     <s v="false"/>
     <n v="200"/>
     <n v="80"/>
@@ -2517,8 +2528,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22F74571-CE72-4261-8FEF-60FD17F1BBF7}" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:G5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{22F74571-CE72-4261-8FEF-60FD17F1BBF7}" name="TablaDinámica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A1:G10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="95">
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
@@ -2549,8 +2560,18 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item sd="0" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2563,17 +2584,17 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
+        <item x="1"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2639,20 +2660,37 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="3">
+  <rowFields count="5">
     <field x="32"/>
     <field x="33"/>
+    <field x="20"/>
+    <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="9">
     <i>
+      <x/>
+    </i>
+    <i r="1">
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -7667,7 +7705,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53541549-81B7-4173-812E-FF7A878E311F}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -7726,71 +7764,186 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>112</v>
+      <c r="A3" s="12">
+        <v>0.05</v>
       </c>
       <c r="B3" s="11">
-        <v>0.53357245674357345</v>
+        <v>0.29984678410375015</v>
       </c>
       <c r="C3" s="11">
-        <v>6.4947069622204295E-3</v>
+        <v>-0.10343591476757004</v>
       </c>
       <c r="D3" s="11">
-        <v>0.61924281401887682</v>
+        <v>0.38913617260058181</v>
       </c>
       <c r="E3" s="11">
-        <v>0.48881540227185899</v>
+        <v>0.22705623606290692</v>
       </c>
       <c r="F3" s="11">
-        <v>0.38676601553751977</v>
+        <v>0.16780297359010771</v>
       </c>
       <c r="G3" s="11">
-        <v>0.63946559514603707</v>
+        <v>0.41539175416140106</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B4" s="11">
-        <v>0.7075758625018197</v>
+        <v>0.53357245674357345</v>
       </c>
       <c r="C4" s="11">
-        <v>2.602171957264441E-2</v>
+        <v>6.4947069622204295E-3</v>
       </c>
       <c r="D4" s="11">
-        <v>0.78800379585407188</v>
+        <v>0.61924281401887682</v>
       </c>
       <c r="E4" s="11">
-        <v>0.68649491545070429</v>
+        <v>0.48881540227185899</v>
       </c>
       <c r="F4" s="11">
-        <v>0.61740672723026058</v>
+        <v>0.38676601553751977</v>
       </c>
       <c r="G4" s="11">
-        <v>0.73839801147224149</v>
+        <v>0.63946559514603707</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0.53357245674357345</v>
+      </c>
+      <c r="C5" s="11">
+        <v>6.4947069622204295E-3</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.61924281401887682</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.48881540227185899</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.38676601553751977</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.63946559514603707</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.53357245674357345</v>
+      </c>
+      <c r="C6" s="11">
+        <v>6.4947069622204295E-3</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.61924281401887682</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.48881540227185899</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.38676601553751977</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.63946559514603707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.7075758625018197</v>
+      </c>
+      <c r="C7" s="11">
+        <v>2.602171957264441E-2</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.78800379585407188</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0.68649491545070429</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.61740672723026058</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.73839801147224149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.7075758625018197</v>
+      </c>
+      <c r="C8" s="11">
+        <v>2.602171957264441E-2</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.78800379585407188</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.68649491545070429</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.61740672723026058</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.73839801147224149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="11">
+        <v>0.7075758625018197</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2.602171957264441E-2</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0.78800379585407188</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.68649491545070429</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.61740672723026058</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.73839801147224149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B10" s="11">
         <v>0.51366503444971445</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C10" s="11">
         <v>-2.3639829410901741E-2</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D10" s="11">
         <v>0.59879426082451015</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E10" s="11">
         <v>0.46745551792848994</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F10" s="11">
         <v>0.39065857211929611</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G10" s="11">
         <v>0.59775178692655984</v>
       </c>
     </row>
